--- a/src/attributions/attributions_ig_traj_302.xlsx
+++ b/src/attributions/attributions_ig_traj_302.xlsx
@@ -1568,22 +1568,22 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.03435453746320331</v>
+        <v>-0.1375419841691328</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4759943227380438</v>
+        <v>0.1282076996082207</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1201594639894182</v>
+        <v>-0.09680788758701989</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -1595,19 +1595,19 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.005775807930814251</v>
+        <v>0.009603994485909043</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2588592995996558</v>
+        <v>0.05103535160769921</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.03853365835707552</v>
+        <v>-0.12180474080804</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
@@ -1622,19 +1622,19 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.03622358152263674</v>
+        <v>-0.02251217827354593</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2485302261703173</v>
+        <v>0.06116620429137454</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.03929969543218494</v>
+        <v>-0.07595381262991278</v>
       </c>
       <c r="X3" t="n">
         <v>-0</v>
@@ -1643,28 +1643,28 @@
         <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.08169980291244344</v>
+        <v>0.07544485018152118</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1444705563325223</v>
+        <v>-0.0911127929953881</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.211631905507813</v>
+        <v>-0.07461031664198584</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
         <v>-0</v>
@@ -1676,106 +1676,106 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.01194594574275511</v>
+        <v>0.008730755982929593</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.08150807587867179</v>
+        <v>-0.09166289759052448</v>
       </c>
       <c r="AN3" t="n">
         <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.1282613914478672</v>
+        <v>-0.1418294395906851</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.09045142658781727</v>
+        <v>-0.1350108992803461</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2375787617720785</v>
+        <v>-0.009262807223944063</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.07998496561280662</v>
+        <v>-0.3832481863971979</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.002146357323769882</v>
+        <v>-0.05148288100394291</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.2552309159334467</v>
+        <v>0.05204698551933999</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.02578993502219108</v>
+        <v>0.1469578918815359</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.06023217023328765</v>
+        <v>0.08228426874032643</v>
       </c>
       <c r="BM3" t="n">
         <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.1940946495368009</v>
+        <v>0.008536523811823505</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.04536711042732002</v>
+        <v>0.02671699778387564</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1784,22 +1784,22 @@
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.007562894209061898</v>
+        <v>-0.1134684608248421</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.03298864393481588</v>
+        <v>0.1090421460806675</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.09669591099923526</v>
+        <v>-0.1081599165817026</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
         <v>-0</v>
@@ -1811,19 +1811,19 @@
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.01439100189716217</v>
+        <v>0.09006039417358441</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.09780634357270909</v>
+        <v>-0.02022742422403931</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.003645915826593462</v>
+        <v>0.09207698833283852</v>
       </c>
       <c r="CI3" t="n">
         <v>-0</v>
@@ -1832,106 +1832,106 @@
         <v>-0</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
         <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.003047177831489872</v>
+        <v>-0.04158852518931353</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0.08252775565730001</v>
+        <v>-0.0141535650425866</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.3970769765209062</v>
+        <v>-0.0493248715921176</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.008016219320154899</v>
+        <v>0.07248632902647885</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.1118768827842311</v>
+        <v>-0.04595026217706461</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.005103569068570612</v>
+        <v>0.03615441998968261</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0.04073465967932579</v>
+        <v>0.04594228523734722</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.009120133466261754</v>
+        <v>0.0003207020815774717</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.01877661324188408</v>
+        <v>0.1923139199130547</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.03951725934306869</v>
+        <v>0.1262715905176426</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.06912117432372802</v>
+        <v>0.05881948163695722</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.1108696402149164</v>
+        <v>-0.09649641934533516</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
@@ -1943,55 +1943,55 @@
         <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.07007600361633561</v>
+        <v>0.02525538625341657</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.1306316238305401</v>
+        <v>0.1710022514965758</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.1782618142599951</v>
+        <v>-0.1287696260191434</v>
       </c>
       <c r="EB3" t="n">
         <v>0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.008558910096247653</v>
+        <v>0.0447426001031852</v>
       </c>
       <c r="EG3" t="n">
         <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.2116875547830959</v>
+        <v>0.01480269877425146</v>
       </c>
       <c r="EI3" t="n">
         <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.04159921834235067</v>
+        <v>0.08681129308943906</v>
       </c>
       <c r="EK3" t="n">
         <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM3" t="n">
         <v>-0</v>
@@ -2000,52 +2000,52 @@
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.06074757165018695</v>
+        <v>0.02224086463488797</v>
       </c>
       <c r="EP3" t="n">
         <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.09386918556968972</v>
+        <v>-0.009177657272764076</v>
       </c>
       <c r="ER3" t="n">
         <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.04838250157991998</v>
+        <v>0.1093812170028477</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.0184441157825004</v>
+        <v>0.06833027625956764</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.1320928299374139</v>
+        <v>-0.05134221294588415</v>
       </c>
       <c r="FA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.002178122174200874</v>
+        <v>0.05814288973903646</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
@@ -2054,25 +2054,25 @@
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.1560292318197838</v>
+        <v>0.2588696792581011</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0.03455305248514875</v>
+        <v>0.0292601803064623</v>
       </c>
       <c r="FJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.01773195163690647</v>
+        <v>-0.03048586237588052</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN3" t="n">
         <v>0</v>
@@ -2081,19 +2081,19 @@
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.1503279883909637</v>
+        <v>0.2034392949531792</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR3" t="n">
-        <v>-0.0005516469418849135</v>
+        <v>0.002305990727709081</v>
       </c>
       <c r="FS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.003021711135958419</v>
+        <v>0.008967052456188103</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
@@ -2105,16 +2105,16 @@
         <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.09156337390444502</v>
+        <v>0.1827343516144728</v>
       </c>
       <c r="FZ3" t="n">
         <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.2547103064914795</v>
+        <v>0.007192897239381083</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
@@ -2123,16 +2123,16 @@
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -2140,16 +2140,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3561149310637874</v>
+        <v>0.2249526320812073</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1265255888044061</v>
+        <v>-0.08272107523130698</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.07198802680510283</v>
+        <v>-0.05806334348074077</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2161,22 +2161,22 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1825301682243356</v>
+        <v>0.1692177165932417</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.03585201400294388</v>
+        <v>-0.03290223596577727</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.05183328611711112</v>
+        <v>-0.0488374769160468</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2185,88 +2185,88 @@
         <v>-0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1249270999519946</v>
+        <v>0.04288307347656744</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01529849920089017</v>
+        <v>-0.03896814415980528</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06474501983557733</v>
+        <v>-0.02416157288533189</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.06264810829151295</v>
+        <v>-0.008574161051329309</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.02789864735587837</v>
+        <v>-0.04970115745472372</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.04827510066501649</v>
+        <v>-0.08338241847656776</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0655387643900939</v>
+        <v>0.110496230490509</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.03736921922498135</v>
+        <v>-0.04647736144904235</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.0368331781294193</v>
+        <v>0.04991998854422401</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,25 +2275,25 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.4593330658165092</v>
+        <v>0.2605894267888146</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.002960269556493977</v>
+        <v>-0.06498010259518466</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1642860309609783</v>
+        <v>-0.1179278590678859</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>-0</v>
@@ -2302,16 +2302,16 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01058398285251737</v>
+        <v>-0.02804627910984446</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.08377110283015082</v>
+        <v>0.005070006191401013</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.1368602223709405</v>
+        <v>-0.03089052703337884</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.05070206617128821</v>
+        <v>0.009709746267504036</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.1006508634624478</v>
+        <v>0.0225137473377172</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.03795953933930902</v>
+        <v>0.07116102845571834</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,25 +2356,25 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1731773461058878</v>
+        <v>0.1344896050385409</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0004475372946568101</v>
+        <v>-0.03897905949792791</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.008385119989591502</v>
+        <v>-0.02149428469150809</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -2383,43 +2383,43 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.07575219459391222</v>
+        <v>-0.08426140058727505</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.01728485347369743</v>
+        <v>0.07158368932262237</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.02943372403463158</v>
+        <v>0.01756833599049491</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.01306412190612003</v>
+        <v>-0.07002339680449547</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.1480232095697516</v>
+        <v>0.1003990502308606</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.1599487314418404</v>
+        <v>0.02680077168207731</v>
       </c>
       <c r="CR4" t="n">
         <v>0</v>
@@ -2437,49 +2437,49 @@
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.06168283758816218</v>
+        <v>-0.0881393090253256</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0443104475796286</v>
+        <v>0.08456688016907175</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.02210503069352294</v>
+        <v>0.02236910615383255</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.04834388103573518</v>
+        <v>-0.05318483417972041</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0.004042982777591294</v>
+        <v>-0.005902090485681268</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.0006603669420508549</v>
+        <v>0.0009026051864645846</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.08497180177957243</v>
+        <v>-0.07019501009321494</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.03747315826602773</v>
+        <v>0.02454245971623014</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.02982821848932385</v>
+        <v>-0.02180398013505939</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
@@ -2518,19 +2518,19 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.05348678516823786</v>
+        <v>0.01217211090085578</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.0651930643485146</v>
+        <v>0.03145492060819784</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.001664440497526358</v>
+        <v>-0.01323691852391613</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
@@ -2539,55 +2539,55 @@
         <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.0237843792028303</v>
+        <v>-0.05064262160798424</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.08049376441311916</v>
+        <v>0.06287095381583942</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.006741574273745052</v>
+        <v>0.02129658351583329</v>
       </c>
       <c r="EK4" t="n">
         <v>-0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.04093176850525554</v>
+        <v>-0.04202429460635008</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.00426669618592571</v>
+        <v>-0.05734362386280926</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.01655311467295086</v>
+        <v>0.001750522582179614</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
@@ -2599,46 +2599,46 @@
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.06614200946667963</v>
+        <v>-0.096598256082535</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.02743098400969963</v>
+        <v>0.07784371812896376</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.03422395504262252</v>
+        <v>0.01139488912415378</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.02234940341817437</v>
+        <v>-0.05403230732250912</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.06563666382333146</v>
+        <v>0.03668896593892575</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.01840826022509459</v>
+        <v>0.009024684883819981</v>
       </c>
       <c r="FL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,28 +2647,28 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.003107583882728665</v>
+        <v>-0.0008905182291499128</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.01344969248240226</v>
+        <v>0.1069802263900754</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0006818895158254737</v>
+        <v>-0.000721481128796628</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW4" t="n">
         <v>0</v>
@@ -2677,39 +2677,39 @@
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.007396112471023683</v>
+        <v>-0.07389562813438912</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.02526066701061019</v>
+        <v>0.03309945970906024</v>
       </c>
       <c r="GC4" t="n">
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1067520881614638</v>
+        <v>0.5846401646874735</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,16 +2718,16 @@
         <v>-0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.06052599988298477</v>
+        <v>0.06748884320076134</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.03846608801114317</v>
+        <v>-0.3057057672873694</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,73 +2736,73 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04964192727147156</v>
+        <v>0.4789779219461908</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0442802221767126</v>
+        <v>-0.06040906687645849</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01551196835625203</v>
+        <v>-0.1225755664590213</v>
       </c>
       <c r="P5" t="n">
         <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01250145826529648</v>
+        <v>0.1482461458832208</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01249850471419778</v>
+        <v>-0.1626798442771478</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02767342172499816</v>
+        <v>0.005535596251839865</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.02388469132956183</v>
+        <v>0.06907708397743623</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.01826901798473594</v>
+        <v>-0.32249566608665</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.01059706986523436</v>
+        <v>-0.03000066824097755</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.02092504024519522</v>
+        <v>0.1788034462929333</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -2826,13 +2826,13 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.02009997719183698</v>
+        <v>0.03485495812329827</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.01727355496840892</v>
+        <v>-0.1143784035683871</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
@@ -2841,10 +2841,10 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.09855310361243265</v>
+        <v>0.7155466085435578</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2853,16 +2853,16 @@
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.04642104072965226</v>
+        <v>-0.2864149596550675</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.01155946554011045</v>
+        <v>-0.2254946193591347</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.04027128200858136</v>
+        <v>0.04939657186401371</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,40 +2880,40 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.03261881706025941</v>
+        <v>-0.04748707701235453</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.01797634261063356</v>
+        <v>-0.149340550317623</v>
       </c>
       <c r="BI5" t="n">
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.05188754683474466</v>
+        <v>0.05195722938296733</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
         <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.02928728955659736</v>
+        <v>0.1346636954232817</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.01123681631801555</v>
+        <v>0.06843000823230508</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.03825805210517411</v>
+        <v>0.3751919635970525</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,97 +2934,97 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.01148512049897203</v>
+        <v>-0.03978882574643581</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.01303028352780599</v>
+        <v>-0.1057308149599697</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>-0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.01897536174469697</v>
+        <v>-0.2185069353278986</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01329747553957948</v>
+        <v>-0.06054126951902113</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.009954338262137805</v>
+        <v>0.1520018343524891</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.01582086210105488</v>
+        <v>-0.3524668650109042</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.0005885399799151856</v>
+        <v>0.1347856632408768</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.0273305265405328</v>
+        <v>0.1517755908989855</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.009502863082208027</v>
+        <v>-0.1995316553174843</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01439833212033915</v>
+        <v>-0.06422944683377119</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.01271295844720441</v>
+        <v>0.1473106606820424</v>
       </c>
       <c r="DB5" t="n">
         <v>-0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
@@ -3033,52 +3033,52 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.01125526900111296</v>
+        <v>-0.0950350970054965</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01141030791665471</v>
+        <v>-0.1830143630375655</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-6.056470297878208e-05</v>
+        <v>0.02285976067688011</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.02797623750353575</v>
+        <v>-0.120514164971408</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.01634930262969177</v>
+        <v>-0.028120163109461</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.01633261051959558</v>
+        <v>0.09697630604348195</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,25 +3087,25 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.006441083044735357</v>
+        <v>-0.007544112190535159</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02630858752039393</v>
+        <v>0.07102010573531786</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.01934566402305272</v>
+        <v>0.07538276345484331</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,52 +3114,52 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.00205751349145509</v>
+        <v>-0.0773667530295807</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.007691282343582714</v>
+        <v>-0.1178071108051539</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.002110384314062909</v>
+        <v>0.06775714948572097</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.005679613723549085</v>
+        <v>-0.06783402523229028</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.01250032474378423</v>
+        <v>-0.1963105586685768</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.02041046235442567</v>
+        <v>0.1693154399202757</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
         <v>0</v>
@@ -3168,34 +3168,34 @@
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.009257979069952214</v>
+        <v>-0.2368799575322932</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01147998931206695</v>
+        <v>-0.09229372422624399</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.01676593326430771</v>
+        <v>0.1215998275770309</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.01751478070731344</v>
+        <v>-0.2965605117487184</v>
       </c>
       <c r="FI5" t="n">
         <v>0</v>
@@ -3204,25 +3204,25 @@
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.030966821181032</v>
+        <v>0.1349442719801187</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01868111649985066</v>
+        <v>0.2344806116669418</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.001266604494608573</v>
+        <v>0.0304016898071971</v>
       </c>
       <c r="FR5" t="n">
         <v>0</v>
@@ -3231,43 +3231,43 @@
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>3.863028141226272e-05</v>
+        <v>-0.007166409920661269</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.01424341838014244</v>
+        <v>0.009255338770036521</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.03099683841162381</v>
+        <v>-0.08066358879397278</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0.01757549923708997</v>
+        <v>0.05963710670371976</v>
       </c>
       <c r="GE5" t="n">
         <v>0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>0</v>
@@ -3844,25 +3844,25 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.6391659145313217</v>
+        <v>0.227338805252194</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2365980492158563</v>
+        <v>-0.2494957970149631</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1113425574134316</v>
+        <v>-0.03080799101212946</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
@@ -3871,19 +3871,19 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3694608138268159</v>
+        <v>0.1843836328035491</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1293568256043511</v>
+        <v>-0.1788781056694458</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1278050197358959</v>
+        <v>-0.0541547130225441</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,88 +3892,88 @@
         <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1925241374079961</v>
+        <v>0.05797938119555512</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.01592377287021692</v>
+        <v>-0.0630735588776105</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06923603100430159</v>
+        <v>-0.09715466272707103</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1654662477341693</v>
+        <v>-0.07425092491691966</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.03861032753436842</v>
+        <v>-0.08341037151108419</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.04613077271413486</v>
+        <v>-0.1120903238950536</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.08679085030393288</v>
+        <v>0.1096284874304437</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.05372001504882036</v>
+        <v>-0.07688509253191995</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.08112050885404522</v>
+        <v>0.02533949150325344</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
@@ -3982,43 +3982,43 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.6608559989016614</v>
+        <v>0.2745460792774411</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.00852837919392384</v>
+        <v>-0.1334024233982571</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1789105404760029</v>
+        <v>-0.2569631951707098</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.04601121809795152</v>
+        <v>-0.03464833342549736</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.0986632030180459</v>
+        <v>-0.07081479480283163</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.2625437831648823</v>
+        <v>0.001844071539576143</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,31 +4027,31 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.1317584643959548</v>
+        <v>0.03465587711087609</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.1276229836939824</v>
+        <v>0.07330073326576034</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.08416168416787762</v>
+        <v>0.05042395207086619</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,25 +4063,25 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2510892411769912</v>
+        <v>0.1398766529654352</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.002205373589976408</v>
+        <v>-0.03773212618171573</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.02344556451889979</v>
+        <v>-0.06249743650177928</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -4090,19 +4090,19 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1285939729541455</v>
+        <v>-0.05398420514938259</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.007282079709320145</v>
+        <v>0.1469384107362045</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.02676603560516585</v>
+        <v>0.02948850571026861</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,22 +4111,22 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.04209217328935084</v>
+        <v>-0.02564566963078294</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.2282899671561038</v>
+        <v>0.2311566627706725</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1925689471241108</v>
+        <v>0.1183551681035574</v>
       </c>
       <c r="CR7" t="n">
         <v>0</v>
@@ -4135,31 +4135,31 @@
         <v>-0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
         <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.09699398560957834</v>
+        <v>-0.05395511879051818</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.05398731966621138</v>
+        <v>0.1662544196480094</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.0463487271341383</v>
+        <v>0.03780934194154881</v>
       </c>
       <c r="DA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,22 +4171,22 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.03328877388133185</v>
+        <v>-0.04066162969709777</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.002808631668574844</v>
+        <v>-0.0122911359865164</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01360289788541093</v>
+        <v>-0.00715503975939125</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
@@ -4198,22 +4198,22 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.1090123320997229</v>
+        <v>-0.05899793133546221</v>
       </c>
       <c r="DP7" t="n">
         <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0004832398363914035</v>
+        <v>0.01723378263722864</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.03803142123141685</v>
+        <v>0.004948240222256394</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
@@ -4225,22 +4225,22 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.04996801098329219</v>
+        <v>0.005479391242077709</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.06850969970172842</v>
+        <v>0.05148191279089112</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.05908075420209195</v>
+        <v>-0.0559483804784536</v>
       </c>
       <c r="EB7" t="n">
         <v>0</v>
       </c>
       <c r="EC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED7" t="n">
         <v>0</v>
@@ -4252,25 +4252,25 @@
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.01979258951332803</v>
+        <v>-0.0370876357035748</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.07846592610125309</v>
+        <v>0.1390947152663113</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.01306731612061468</v>
+        <v>0.01744479158162301</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
@@ -4279,22 +4279,22 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.0818442401640978</v>
+        <v>-0.006422260458337299</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.007976905882326083</v>
+        <v>-0.1494561784050528</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.03426789878111721</v>
+        <v>-0.03391909493978424</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,73 +4306,73 @@
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1055352385274809</v>
+        <v>-0.06477919402033414</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.02494450854299121</v>
+        <v>0.1679951997507485</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.03277959337011766</v>
+        <v>0.01575354362179768</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.01582168562076832</v>
+        <v>-0.04173305016860139</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.1013031385400235</v>
+        <v>0.07812157017115978</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02667687198180682</v>
+        <v>-0.002125382144652045</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN7" t="n">
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.01321612539136583</v>
+        <v>-0.01762941276570488</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.07227116730846736</v>
+        <v>0.1544093554705217</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.01636606412371233</v>
+        <v>-0.03979478997808469</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
@@ -4381,31 +4381,31 @@
         <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.0005382724481232909</v>
+        <v>-0.06921089039341392</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.09304818465139206</v>
+        <v>0.1227721408872927</v>
       </c>
       <c r="GC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>-0</v>
@@ -4985,22 +4985,22 @@
         <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.1610482492955126</v>
+        <v>-0.199119652468921</v>
       </c>
       <c r="C9" t="n">
         <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1088077813123832</v>
+        <v>0.05888995757500497</v>
       </c>
       <c r="F9" t="n">
-        <v>0.852135809887519</v>
+        <v>0.3288254141689525</v>
       </c>
       <c r="G9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1024361407059045</v>
+        <v>-0.1407182321511523</v>
       </c>
       <c r="L9" t="n">
         <v>-0</v>
@@ -5021,25 +5021,25 @@
         <v>-0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.184853148335681</v>
+        <v>0.1009990488051161</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5912815174291575</v>
+        <v>0.2506825452931284</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.08713665918561626</v>
+        <v>-0.0789867030410563</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
@@ -5048,37 +5048,37 @@
         <v>-0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1213692006488572</v>
+        <v>0.07574890129642413</v>
       </c>
       <c r="X9" t="n">
-        <v>0.07558953622967299</v>
+        <v>-0.01714807244127299</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01661956448096112</v>
+        <v>-0.02611488186154879</v>
       </c>
       <c r="AD9" t="n">
         <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.08723902682970272</v>
+        <v>0.1724049325548217</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.08411596508441901</v>
+        <v>0.05590913341762901</v>
       </c>
       <c r="AH9" t="n">
         <v>-0</v>
@@ -5087,109 +5087,109 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK9" t="n">
         <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0008455007996129903</v>
+        <v>-0.09336528384906741</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN9" t="n">
         <v>-0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.04608662049986035</v>
+        <v>-0.02099230398620305</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.09422851899599061</v>
+        <v>0.05647995009816794</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.1338794208973295</v>
+        <v>-0.3917043991708735</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1260114726681031</v>
+        <v>0.09362346584371398</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.4660836145210936</v>
+        <v>0.1063786849749006</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
         <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.1324941364813479</v>
+        <v>0.06517419177599296</v>
       </c>
       <c r="BE9" t="n">
         <v>-0</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.03953896381186277</v>
+        <v>0.1986576642863446</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.2581850863709914</v>
+        <v>0.09979472769201064</v>
       </c>
       <c r="BI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
         <v>0</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>-0.1195051085225597</v>
+        <v>-0.03074643060944326</v>
       </c>
       <c r="BN9" t="n">
         <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>-0.06796066888769144</v>
+        <v>-0.0420021140001457</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.08185331599208102</v>
+        <v>-0.0355957147200106</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5198,25 +5198,25 @@
         <v>-0</v>
       </c>
       <c r="BU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>-0.005180521933065721</v>
+        <v>-0.0872086789034576</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.04456770699322429</v>
+        <v>0.02506263236749218</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.2434810026973603</v>
+        <v>0.06236255227459042</v>
       </c>
       <c r="CA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
@@ -5228,46 +5228,46 @@
         <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0277157000295098</v>
+        <v>0.07311869708452651</v>
       </c>
       <c r="CF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.02592193181401367</v>
+        <v>-0.03708223376533667</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0.1475561910661542</v>
+        <v>-0.08982222756610743</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>-0</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.01659900254786662</v>
+        <v>0.0864534286968181</v>
       </c>
       <c r="CO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.2359128661003942</v>
+        <v>-0.2409808996918028</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.034721434681577</v>
+        <v>0.02956641261525401</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5276,28 +5276,28 @@
         <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.02097548525353573</v>
+        <v>0.06730597538314344</v>
       </c>
       <c r="CX9" t="n">
         <v>-0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.002695054673284479</v>
+        <v>-0.04599392597895086</v>
       </c>
       <c r="DA9" t="n">
-        <v>-0.1392592744831578</v>
+        <v>-0.08953212714097293</v>
       </c>
       <c r="DB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
         <v>0</v>
@@ -5306,10 +5306,10 @@
         <v>-0</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.04330872081444261</v>
+        <v>0.06239196176542462</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
@@ -5318,40 +5318,40 @@
         <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.1874260218333113</v>
+        <v>0.1220495816818856</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.008214384681277746</v>
+        <v>-0.03247686991478021</v>
       </c>
       <c r="DK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL9" t="n">
         <v>-0</v>
       </c>
       <c r="DM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.0197887322422685</v>
+        <v>0.01868053101601601</v>
       </c>
       <c r="DP9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ9" t="n">
         <v>-0</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.04523500524884511</v>
+        <v>0.05094041507888031</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.02628798538146674</v>
+        <v>-0.034327733487344</v>
       </c>
       <c r="DT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
@@ -5363,103 +5363,103 @@
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0347474500393013</v>
+        <v>-0.01548782615230276</v>
       </c>
       <c r="DY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ9" t="n">
         <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.01870869682630657</v>
+        <v>0.009989404814657543</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0.1080636860403735</v>
+        <v>0.02972150094483624</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.005247344624829083</v>
+        <v>0.03429690136284677</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.009843867366044413</v>
+        <v>0.02010931154755789</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0.1400175333316397</v>
+        <v>-0.06392203553445427</v>
       </c>
       <c r="EL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.07326980897088098</v>
+        <v>0.0374355143781172</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
         <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0001531781887074864</v>
+        <v>-0.03695478209112832</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.03072216720621433</v>
+        <v>0.1433001859493042</v>
       </c>
       <c r="EU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV9" t="n">
         <v>-0</v>
       </c>
       <c r="EW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX9" t="n">
         <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.01205610375827625</v>
+        <v>0.07857870187734378</v>
       </c>
       <c r="EZ9" t="n">
         <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.0193933865953363</v>
+        <v>-0.02949688323444401</v>
       </c>
       <c r="FC9" t="n">
-        <v>-0.1370084400539949</v>
+        <v>-0.08864298241716138</v>
       </c>
       <c r="FD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE9" t="n">
         <v>-0</v>
@@ -5471,7 +5471,7 @@
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.01434229979076404</v>
+        <v>0.09386934754016683</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
@@ -5480,16 +5480,16 @@
         <v>0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.008228703632391506</v>
+        <v>-0.0941705322346595</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0.1013887211656837</v>
+        <v>-0.04983279476789006</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
         <v>-0</v>
@@ -5498,19 +5498,19 @@
         <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.01416855702095217</v>
+        <v>0.009464583894530596</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.06405269207446466</v>
+        <v>0.07164158885454028</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0.2130015639146429</v>
+        <v>0.004488155756414152</v>
       </c>
       <c r="FV9" t="n">
         <v>0</v>
@@ -5522,13 +5522,13 @@
         <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0403298462270776</v>
+        <v>0.1186616016292991</v>
       </c>
       <c r="GA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB9" t="n">
         <v>0</v>
@@ -5537,10 +5537,10 @@
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.02325825215476452</v>
+        <v>0.03732270316352415</v>
       </c>
       <c r="GE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF9" t="n">
         <v>-0</v>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9275831773675681</v>
+        <v>0.4846689503283536</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5563,13 +5563,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0006543958195979888</v>
+        <v>0.01626953667917182</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.15031659964763</v>
+        <v>-0.3108168111793189</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
         <v>-0</v>
@@ -5581,34 +5581,34 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6828209255984037</v>
+        <v>0.5090918859781465</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.07086726417465244</v>
+        <v>-0.1797669613170653</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8953381462463568</v>
+        <v>-0.3311427428524321</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
         <v>-0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.07280808561817999</v>
+        <v>0.1232122969791848</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -5617,43 +5617,43 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0914036260287084</v>
+        <v>-0.03075297933484361</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1859628724526209</v>
+        <v>-0.06134344458557314</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1788746113347457</v>
+        <v>0.05546810775694425</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.06548548976914412</v>
+        <v>-0.2050179809068968</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.104037955729008</v>
+        <v>-0.08531181982172321</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
         <v>-0</v>
@@ -5662,22 +5662,22 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.07855909347610547</v>
+        <v>0.1758671416141064</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.1276192559349635</v>
+        <v>0.04641213244083675</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.2228388324644296</v>
+        <v>-0.1090358396139752</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
@@ -5686,22 +5686,22 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.5556158566651179</v>
+        <v>0.6623033510915838</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.005196984851097001</v>
+        <v>-0.1916413560623693</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.845476900926435</v>
+        <v>-0.248869031003847</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -5713,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.1883257353102635</v>
+        <v>-0.2022342838898059</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,13 +5725,13 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1343122508573107</v>
+        <v>-0.0587773469560686</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.2026003116894441</v>
+        <v>0.001804152218583883</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
         <v>-0</v>
@@ -5740,10 +5740,10 @@
         <v>-0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.2062694120227166</v>
+        <v>-0.01100207208803755</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,25 +5752,25 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>-0.02372948108130291</v>
+        <v>0.05384623623999147</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0.1441044411051978</v>
+        <v>0.04980350247766285</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT10" t="n">
         <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.3213255545467614</v>
+        <v>0.3584790248432173</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
@@ -5779,13 +5779,13 @@
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.04343537188163908</v>
+        <v>-0.09035129937017283</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.4091961499661679</v>
+        <v>-0.1587462029556798</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB10" t="n">
         <v>-0</v>
@@ -5794,55 +5794,55 @@
         <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.1795711014328786</v>
+        <v>-0.1687793587084231</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.003291060756764263</v>
+        <v>0.0341966723639253</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.16184330870681</v>
+        <v>0.0915476944628438</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.01645160525887287</v>
+        <v>-0.1196535872207301</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.1595941004207705</v>
+        <v>0.2211097476038334</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.002237903322447016</v>
+        <v>0.113748198145155</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
         <v>-0</v>
@@ -5851,22 +5851,22 @@
         <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.1527078887252293</v>
+        <v>-0.1516622476679713</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.02166459087406845</v>
+        <v>0.02868083994990873</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.1693115239255667</v>
+        <v>0.113437998073797</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
         <v>-0</v>
@@ -5878,34 +5878,34 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.2031082442774068</v>
+        <v>-0.09376583096332608</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
         <v>-0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.09188838320631414</v>
+        <v>-0.1008403890235361</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.3920880790026316</v>
+        <v>0.04817777115490777</v>
       </c>
       <c r="DK10" t="n">
         <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.07786345027817719</v>
+        <v>-0.03481943529716088</v>
       </c>
       <c r="DP10" t="n">
         <v>0</v>
@@ -5914,13 +5914,13 @@
         <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01386198428969668</v>
+        <v>-0.01256829309166897</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.1470012641283373</v>
+        <v>0.08819148385813103</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
         <v>-0</v>
@@ -5932,52 +5932,52 @@
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.1170105724663654</v>
+        <v>-0.04488576163023281</v>
       </c>
       <c r="DY10" t="n">
         <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.08890680398345086</v>
+        <v>-0.04805383301285415</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.1498868042846061</v>
+        <v>0.004772968895031772</v>
       </c>
       <c r="EC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED10" t="n">
         <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.09873366804959559</v>
+        <v>-0.08269220550169236</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.05321231750002578</v>
+        <v>-0.04068773939969844</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.02248494541082693</v>
+        <v>-0.01845814354863081</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
@@ -5986,7 +5986,7 @@
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.09478674268997729</v>
+        <v>0.09227286554356921</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
@@ -5995,52 +5995,52 @@
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.02553130058808267</v>
+        <v>0.05534059741187628</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0.1164341345172164</v>
+        <v>0.04408148215272718</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.1513224572845659</v>
+        <v>-0.174944787682358</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.00171139917553017</v>
+        <v>-0.009814087217785263</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.1512176811955386</v>
+        <v>0.09453740619452841</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
         <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.03647256348186501</v>
+        <v>-0.1551058626451968</v>
       </c>
       <c r="FI10" t="n">
         <v>0</v>
@@ -6049,10 +6049,10 @@
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.07876847655651834</v>
+        <v>0.09402333800998385</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.1787993947286605</v>
+        <v>0.1736701716411923</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
@@ -6067,19 +6067,19 @@
         <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.04470970028295023</v>
+        <v>-0.1862002570215003</v>
       </c>
       <c r="FR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS10" t="n">
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.2591538159409791</v>
+        <v>0.1016800094058979</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.2177744529922922</v>
+        <v>-0.09193628002065764</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
@@ -6088,31 +6088,31 @@
         <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.05930425694262565</v>
+        <v>-0.03346138752108715</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.1077945291504715</v>
+        <v>0.03539668125974697</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
         <v>0</v>
